--- a/Plantilla_Catalogos_GRTVM_ZOTP.xlsx
+++ b/Plantilla_Catalogos_GRTVM_ZOTP.xlsx
@@ -16,18 +16,12 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Condición operativa" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Equipos'!$A$3:$A$4</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="1">'Equipos'!$1:$3</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Protecciones'!$A$3:$A$4</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="2">'Protecciones'!$1:$3</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Eventos'!$A$3:$A$4</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="3">'Eventos'!$1:$3</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Causas'!$A$3:$A$4</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="4">'Causas'!$1:$3</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Subestaciones'!$A$3:$B$4</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="5">'Subestaciones'!$1:$3</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Equipos'!$A$3:$A$3</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Protecciones'!$A$3:$A$3</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Eventos'!$A$3:$A$3</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Causas'!$A$3:$A$3</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Subestaciones'!$A$3:$B$3</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Condición operativa'!$A$3:$A$5</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="6">'Condición operativa'!$1:$3</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -124,7 +118,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="3">
+  <borders count="5">
     <border>
       <left/>
       <right/>
@@ -138,6 +132,29 @@
       </bottom>
     </border>
     <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color rgb="00008C69"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <bottom style="thin">
+        <color rgb="00D9E2F3"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00D9E2F3"/>
+      </left>
+      <right style="thin">
+        <color rgb="00D9E2F3"/>
+      </right>
+      <top style="thin">
+        <color rgb="00D9E2F3"/>
+      </top>
       <bottom style="thin">
         <color rgb="00D9E2F3"/>
       </bottom>
@@ -146,32 +163,33 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -247,67 +265,6 @@
     </indexedColors>
   </colors>
 </styleSheet>
-</file>
-
-<file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="TblEquipos" displayName="TblEquipos" ref="A3:A3" headerRowCount="1">
-  <autoFilter ref="A3:A3"/>
-  <tableColumns count="1">
-    <tableColumn id="1" name="Equipo"/>
-  </tableColumns>
-  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
-</table>
-</file>
-
-<file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="TblProtecciones" displayName="TblProtecciones" ref="A3:A3" headerRowCount="1">
-  <autoFilter ref="A3:A3"/>
-  <tableColumns count="1">
-    <tableColumn id="1" name="Protección"/>
-  </tableColumns>
-  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
-</table>
-</file>
-
-<file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="TblEventos" displayName="TblEventos" ref="A3:A3" headerRowCount="1">
-  <autoFilter ref="A3:A3"/>
-  <tableColumns count="1">
-    <tableColumn id="1" name="Evento / disparo"/>
-  </tableColumns>
-  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
-</table>
-</file>
-
-<file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="TblCausas" displayName="TblCausas" ref="A3:A3" headerRowCount="1">
-  <autoFilter ref="A3:A3"/>
-  <tableColumns count="1">
-    <tableColumn id="1" name="Causa"/>
-  </tableColumns>
-  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
-</table>
-</file>
-
-<file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="5" name="TblSubestaciones" displayName="TblSubestaciones" ref="A3:B3" headerRowCount="1">
-  <autoFilter ref="A3:B3"/>
-  <tableColumns count="2">
-    <tableColumn id="1" name="Acrónimo"/>
-    <tableColumn id="2" name="Descripción"/>
-  </tableColumns>
-  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
-</table>
-</file>
-
-<file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="6" name="TblCondicinoperativa" displayName="TblCondicinoperativa" ref="A3:A5" headerRowCount="1">
-  <autoFilter ref="A3:A5"/>
-  <tableColumns count="1">
-    <tableColumn id="1" name="Condición operativa"/>
-  </tableColumns>
-  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
-</table>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -599,15 +556,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F9"/>
+  <dimension ref="A1:B9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="27" customWidth="1" min="1" max="1"/>
-    <col width="25" customWidth="1" min="2" max="2"/>
-    <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="20" customWidth="1" min="4" max="4"/>
-    <col width="20" customWidth="1" min="5" max="5"/>
-    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="34" customWidth="1" min="1" max="1"/>
+    <col width="105" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1" ht="34" customHeight="1">
@@ -616,96 +569,91 @@
           <t>PLANTILLA DE CATÁLOGOS | GRTVM – ZOTP</t>
         </is>
       </c>
-    </row>
-    <row r="2" ht="24" customHeight="1">
-      <c r="A2" s="2" t="inlineStr">
+      <c r="B1" s="2" t="n"/>
+    </row>
+    <row r="2" ht="25" customHeight="1">
+      <c r="A2" s="3" t="inlineStr">
         <is>
           <t>Generador de Mensajes Operativos · Formato de captura e importación</t>
         </is>
       </c>
     </row>
     <row r="4" ht="38" customHeight="1">
-      <c r="A4" s="3" t="inlineStr">
+      <c r="A4" s="4" t="inlineStr">
         <is>
           <t>1. Cómo usar esta plantilla</t>
         </is>
       </c>
-      <c r="B4" s="4" t="inlineStr">
+      <c r="B4" s="5" t="inlineStr">
         <is>
           <t>Captura los datos en la hoja del catálogo correspondiente. No cambies los nombres de las pestañas ni los encabezados de la fila 1.</t>
         </is>
       </c>
     </row>
     <row r="5" ht="38" customHeight="1">
-      <c r="A5" s="3" t="inlineStr">
+      <c r="A5" s="4" t="inlineStr">
         <is>
           <t>2. Importar a la aplicación</t>
         </is>
       </c>
-      <c r="B5" s="4" t="inlineStr">
+      <c r="B5" s="5" t="inlineStr">
         <is>
           <t>Guarda el archivo como .xlsx y utiliza Catálogos → Importar Excel. La aplicación leerá cada pestaña para completar el catálogo correspondiente.</t>
         </is>
       </c>
     </row>
     <row r="6" ht="38" customHeight="1">
-      <c r="A6" s="3" t="inlineStr">
+      <c r="A6" s="4" t="inlineStr">
         <is>
           <t>3. Evitar errores</t>
         </is>
       </c>
-      <c r="B6" s="4" t="inlineStr">
+      <c r="B6" s="5" t="inlineStr">
         <is>
           <t>No combines celdas dentro de las tablas. Escribe un registro por fila y evita filas vacías entre registros.</t>
         </is>
       </c>
     </row>
     <row r="7" ht="38" customHeight="1">
-      <c r="A7" s="3" t="inlineStr">
+      <c r="A7" s="4" t="inlineStr">
         <is>
           <t>4. Subestaciones</t>
         </is>
       </c>
-      <c r="B7" s="4" t="inlineStr">
+      <c r="B7" s="5" t="inlineStr">
         <is>
           <t>En la hoja Subestaciones captura Acrónimo y Descripción en columnas separadas.</t>
         </is>
       </c>
     </row>
     <row r="8" ht="38" customHeight="1">
-      <c r="A8" s="3" t="inlineStr">
+      <c r="A8" s="4" t="inlineStr">
         <is>
           <t>5. Valores predeterminados</t>
         </is>
       </c>
-      <c r="B8" s="4" t="inlineStr">
+      <c r="B8" s="5" t="inlineStr">
         <is>
           <t>Disparo y Se investiga son valores predeterminados del formulario; no es necesario agregarlos al catálogo si no los deseas en tus opciones.</t>
         </is>
       </c>
     </row>
     <row r="9" ht="38" customHeight="1">
-      <c r="A9" s="3" t="inlineStr">
+      <c r="A9" s="4" t="inlineStr">
         <is>
           <t>6. Condición operativa</t>
         </is>
       </c>
-      <c r="B9" s="4" t="inlineStr">
+      <c r="B9" s="5" t="inlineStr">
         <is>
           <t>Se incluyen dos ejemplos editables: normales de operación y condiciones anormales de operación.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="8">
-    <mergeCell ref="B4:F4"/>
-    <mergeCell ref="A2:F2"/>
-    <mergeCell ref="B7:F7"/>
-    <mergeCell ref="B6:F6"/>
-    <mergeCell ref="A1:F1"/>
-    <mergeCell ref="B5:F5"/>
-    <mergeCell ref="B8:F8"/>
-    <mergeCell ref="B9:F9"/>
+  <mergeCells count="2">
+    <mergeCell ref="A2:B2"/>
+    <mergeCell ref="A1:B1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -714,6 +662,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
+    <tabColor rgb="002F5597"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
@@ -724,43 +673,37 @@
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
-      <c r="A1" s="5" t="inlineStr">
+      <c r="A1" s="6" t="inlineStr">
         <is>
           <t>CATÁLOGO: EQUIPOS</t>
         </is>
       </c>
     </row>
-    <row r="2" ht="22" customHeight="1">
-      <c r="A2" s="6" t="inlineStr">
+    <row r="2" ht="23" customHeight="1">
+      <c r="A2" s="7" t="inlineStr">
         <is>
           <t>Capture un registro por fila. No modifique los encabezados.</t>
         </is>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" s="7" t="inlineStr">
+    <row r="3" ht="25" customHeight="1">
+      <c r="A3" s="8" t="inlineStr">
         <is>
           <t>Equipo</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A3:A4"/>
-  <mergeCells count="2">
-    <mergeCell ref="A2"/>
-    <mergeCell ref="A1"/>
-  </mergeCells>
+  <autoFilter ref="A3:A3"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup orientation="landscape" fitToWidth="1"/>
-  <tableParts count="1">
-    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
-  </tableParts>
+  <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
+    <tabColor rgb="002F5597"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
@@ -771,43 +714,37 @@
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
-      <c r="A1" s="5" t="inlineStr">
+      <c r="A1" s="6" t="inlineStr">
         <is>
           <t>CATÁLOGO: PROTECCIONES</t>
         </is>
       </c>
     </row>
-    <row r="2" ht="22" customHeight="1">
-      <c r="A2" s="6" t="inlineStr">
+    <row r="2" ht="23" customHeight="1">
+      <c r="A2" s="7" t="inlineStr">
         <is>
           <t>Capture un registro por fila. No modifique los encabezados.</t>
         </is>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" s="7" t="inlineStr">
+    <row r="3" ht="25" customHeight="1">
+      <c r="A3" s="8" t="inlineStr">
         <is>
           <t>Protección</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A3:A4"/>
-  <mergeCells count="2">
-    <mergeCell ref="A2"/>
-    <mergeCell ref="A1"/>
-  </mergeCells>
+  <autoFilter ref="A3:A3"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup orientation="landscape" fitToWidth="1"/>
-  <tableParts count="1">
-    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
-  </tableParts>
+  <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
+    <tabColor rgb="002F5597"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
@@ -818,43 +755,37 @@
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
-      <c r="A1" s="5" t="inlineStr">
+      <c r="A1" s="6" t="inlineStr">
         <is>
           <t>CATÁLOGO: EVENTOS</t>
         </is>
       </c>
     </row>
-    <row r="2" ht="22" customHeight="1">
-      <c r="A2" s="6" t="inlineStr">
+    <row r="2" ht="23" customHeight="1">
+      <c r="A2" s="7" t="inlineStr">
         <is>
           <t>Capture un registro por fila. No modifique los encabezados.</t>
         </is>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" s="7" t="inlineStr">
+    <row r="3" ht="25" customHeight="1">
+      <c r="A3" s="8" t="inlineStr">
         <is>
           <t>Evento / disparo</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A3:A4"/>
-  <mergeCells count="2">
-    <mergeCell ref="A2"/>
-    <mergeCell ref="A1"/>
-  </mergeCells>
+  <autoFilter ref="A3:A3"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup orientation="landscape" fitToWidth="1"/>
-  <tableParts count="1">
-    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
-  </tableParts>
+  <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
+    <tabColor rgb="002F5597"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
@@ -865,96 +796,84 @@
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
-      <c r="A1" s="5" t="inlineStr">
+      <c r="A1" s="6" t="inlineStr">
         <is>
           <t>CATÁLOGO: CAUSAS</t>
         </is>
       </c>
     </row>
-    <row r="2" ht="22" customHeight="1">
-      <c r="A2" s="6" t="inlineStr">
+    <row r="2" ht="23" customHeight="1">
+      <c r="A2" s="7" t="inlineStr">
         <is>
           <t>Capture un registro por fila. No modifique los encabezados.</t>
         </is>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" s="7" t="inlineStr">
+    <row r="3" ht="25" customHeight="1">
+      <c r="A3" s="8" t="inlineStr">
         <is>
           <t>Causa</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A3:A4"/>
-  <mergeCells count="2">
-    <mergeCell ref="A2"/>
-    <mergeCell ref="A1"/>
-  </mergeCells>
+  <autoFilter ref="A3:A3"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup orientation="landscape" fitToWidth="1"/>
-  <tableParts count="1">
-    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
-  </tableParts>
+  <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
+    <tabColor rgb="002F5597"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:B3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="30" customWidth="1" min="1" max="1"/>
-    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="1" max="1"/>
+    <col width="48" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
-      <c r="A1" s="5" t="inlineStr">
+      <c r="A1" s="6" t="inlineStr">
         <is>
           <t>CATÁLOGO: SUBESTACIONES</t>
         </is>
       </c>
     </row>
-    <row r="2" ht="22" customHeight="1">
-      <c r="A2" s="6" t="inlineStr">
+    <row r="2" ht="23" customHeight="1">
+      <c r="A2" s="7" t="inlineStr">
         <is>
           <t>Capture un registro por fila. No modifique los encabezados.</t>
         </is>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" s="7" t="inlineStr">
+    <row r="3" ht="25" customHeight="1">
+      <c r="A3" s="8" t="inlineStr">
         <is>
           <t>Acrónimo</t>
         </is>
       </c>
-      <c r="B3" s="7" t="inlineStr">
+      <c r="B3" s="8" t="inlineStr">
         <is>
           <t>Descripción</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A3:B4"/>
-  <mergeCells count="2">
-    <mergeCell ref="A2:B2"/>
-    <mergeCell ref="A1:B1"/>
-  </mergeCells>
+  <autoFilter ref="A3:B3"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup orientation="landscape" fitToWidth="1"/>
-  <tableParts count="1">
-    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
-  </tableParts>
+  <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
+    <tabColor rgb="002F5597"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
@@ -965,35 +884,35 @@
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
-      <c r="A1" s="5" t="inlineStr">
+      <c r="A1" s="6" t="inlineStr">
         <is>
           <t>CATÁLOGO: CONDICIÓN OPERATIVA</t>
         </is>
       </c>
     </row>
-    <row r="2" ht="22" customHeight="1">
-      <c r="A2" s="6" t="inlineStr">
+    <row r="2" ht="23" customHeight="1">
+      <c r="A2" s="7" t="inlineStr">
         <is>
           <t>Capture un registro por fila. No modifique los encabezados.</t>
         </is>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" s="7" t="inlineStr">
+    <row r="3" ht="25" customHeight="1">
+      <c r="A3" s="8" t="inlineStr">
         <is>
           <t>Condición operativa</t>
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" s="8" t="inlineStr">
+    <row r="4" ht="22" customHeight="1">
+      <c r="A4" s="9" t="inlineStr">
         <is>
           <t>normales de operación</t>
         </is>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" s="9" t="inlineStr">
+    <row r="5" ht="22" customHeight="1">
+      <c r="A5" s="10" t="inlineStr">
         <is>
           <t>condiciones anormales de operación</t>
         </is>
@@ -1001,14 +920,7 @@
     </row>
   </sheetData>
   <autoFilter ref="A3:A5"/>
-  <mergeCells count="2">
-    <mergeCell ref="A2"/>
-    <mergeCell ref="A1"/>
-  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup orientation="landscape" fitToWidth="1"/>
-  <tableParts count="1">
-    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
-  </tableParts>
+  <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
 </file>